--- a/CAB320 Work Split.xlsx
+++ b/CAB320 Work Split.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connectqutedu-my.sharepoint.com/personal/n11285915_qut_edu_au/Documents/YR5 SEM1/CAB320/ASSESSMENTS/Assessment 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connectqutedu-my.sharepoint.com/personal/n11285915_qut_edu_au/Documents/Documents/GitHub/CAB320-A2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B585E8A-2441-4AC6-A55D-430ECA22D83B}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADC4830A-9E40-4E97-9EDC-B14FC5029E50}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="2040" windowWidth="22605" windowHeight="18570" xr2:uid="{15607E00-DA60-4B2F-9045-4CB7BAC65E04}"/>
+    <workbookView xWindow="5250" yWindow="17070" windowWidth="28800" windowHeight="15345" xr2:uid="{15607E00-DA60-4B2F-9045-4CB7BAC65E04}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,6 +71,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t xml:space="preserve">Joshua George </t>
+  </si>
+  <si>
     <t>Task 2: Code</t>
   </si>
   <si>
@@ -103,44 +106,50 @@
     <t>All image data and labels load correctly with no errors</t>
   </si>
   <si>
-    <t>TBD</t>
+    <t>18-21 JUL</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Task 3a: Code</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>split_data(X, Y, train_fraction, randomize=False, eval_set=True)</t>
+    </r>
+  </si>
+  <si>
+    <t>Output showing train, validation, and test set sizes</t>
+  </si>
+  <si>
+    <t>Function returns correct split datasets in the expected structure</t>
+  </si>
+  <si>
+    <t>Task 3b: Report</t>
+  </si>
+  <si>
+    <t>Explain the split strategy and class balance</t>
+  </si>
+  <si>
+    <t>Markdown explanation plus class distribution table for train/validation/test</t>
+  </si>
+  <si>
+    <t>Explanation clearly justifies that the split is reasonable and does not introduce class imbalance</t>
+  </si>
+  <si>
+    <t>27-29 JUL</t>
   </si>
   <si>
     <t>Not started</t>
-  </si>
-  <si>
-    <t>Task 3a: Code</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Implement </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>split_data(X, Y, train_fraction, randomize=False, eval_set=True)</t>
-    </r>
-  </si>
-  <si>
-    <t>Output showing train, validation, and test set sizes</t>
-  </si>
-  <si>
-    <t>Function returns correct split datasets in the expected structure</t>
-  </si>
-  <si>
-    <t>Task 3b: Report</t>
-  </si>
-  <si>
-    <t>Explain the split strategy and class balance</t>
-  </si>
-  <si>
-    <t>Markdown explanation plus class distribution table for train/validation/test</t>
-  </si>
-  <si>
-    <t>Explanation clearly justifies that the split is reasonable and does not introduce class imbalance</t>
   </si>
   <si>
     <t>Task 4: Code</t>
@@ -198,32 +207,12 @@
     <t>Task 6b: Report</t>
   </si>
   <si>
-    <t>Markdown explanation of frozen MobileNetV2 layers, classifier head, compile step, and training step</t>
-  </si>
-  <si>
-    <t>Reader can understand the function workflow without needing to decode the whole function</t>
-  </si>
-  <si>
-    <t>Task 14: Report</t>
-  </si>
-  <si>
-    <t>Write the final technical conclusion</t>
-  </si>
-  <si>
-    <t>Markdown conclusion recommending learning rate, momentum, model approach, limitations, and future work</t>
-  </si>
-  <si>
-    <t>Conclusion references actual experiment results from the notebook</t>
-  </si>
-  <si>
-    <t>Task 6a: Code</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Implement baseline </t>
-    </r>
-    <r>
-      <rPr>
+    <r>
+      <t xml:space="preserve">Explain how </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
@@ -232,54 +221,76 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> training using SGD</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Training output/history using </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>learning_rate=0.01</t>
-    </r>
+      <t xml:space="preserve"> works</t>
+    </r>
+  </si>
+  <si>
+    <t>Markdown explanation of frozen MobileNetV2 layers, classifier head, compile step, and training step</t>
+  </si>
+  <si>
+    <t>Reader can understand the function workflow without needing to decode the whole function</t>
+  </si>
+  <si>
+    <t>Task 14: Report</t>
+  </si>
+  <si>
+    <t>Write the final technical conclusion</t>
+  </si>
+  <si>
+    <t>Markdown conclusion recommending learning rate, momentum, model approach, limitations, and future work</t>
+  </si>
+  <si>
+    <t>Conclusion references actual experiment results from the notebook</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Joshua Oates</t>
+  </si>
+  <si>
+    <t>Task 6a: Code</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">Implement baseline </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>momentum=0.0</t>
+      <t>transfer_learning()</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve"> training using SGD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Training output/history using </t>
     </r>
     <r>
       <rPr>
@@ -287,53 +298,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>nesterov=False</t>
-    </r>
-  </si>
-  <si>
-    <t>Baseline model trains successfully and returns usable history/results</t>
-  </si>
-  <si>
-    <t>Task 7a: Code</t>
-  </si>
-  <si>
-    <t>Plot training and validation accuracy/error for standard transfer learning</t>
-  </si>
-  <si>
-    <t>Accuracy and loss/error plots with labels, legends, and titles</t>
-  </si>
-  <si>
-    <t>Plots are readable and clearly show training vs validation behaviour</t>
-  </si>
-  <si>
-    <t>Task 7b: Report</t>
-  </si>
-  <si>
-    <t>Interpret the baseline training plots</t>
-  </si>
-  <si>
-    <t>Markdown comment on learning trend, overfitting/underfitting, and validation behaviour</t>
-  </si>
-  <si>
-    <t>Comment directly refers to the plotted results</t>
-  </si>
-  <si>
-    <t>Task 8a: Code</t>
-  </si>
-  <si>
-    <t>Run 3 learning-rate experiments across different orders of magnitude</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Results table/plot for 3 learning rates, e.g. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>0.1</t>
+      <t>learning_rate=0.01</t>
     </r>
     <r>
       <rPr>
@@ -351,7 +316,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>0.01</t>
+      <t>momentum=0.0</t>
     </r>
     <r>
       <rPr>
@@ -369,69 +334,48 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>0.001</t>
-    </r>
-  </si>
-  <si>
-    <t>All three learning-rate runs complete and are comparable</t>
-  </si>
-  <si>
-    <t>Task 8b: Report</t>
-  </si>
-  <si>
-    <t>Discuss learning-rate experiment results</t>
-  </si>
-  <si>
-    <t>Markdown comparison of the 3 learning rates</t>
-  </si>
-  <si>
-    <t>Best learning rate is clearly selected using evidence from results</t>
-  </si>
-  <si>
-    <t>Task 9: Code</t>
-  </si>
-  <si>
-    <t>Evaluate best learning-rate model on the test set and generate confusion matrix</t>
-  </si>
-  <si>
-    <t>Confusion matrix with class labels</t>
-  </si>
-  <si>
-    <t>Confusion matrix displays correct and incorrect predictions for all 5 classes</t>
-  </si>
-  <si>
-    <t>Task 10b: Report</t>
-  </si>
-  <si>
-    <t>Interpret confusion matrix and classification results</t>
-  </si>
-  <si>
-    <t>Markdown comment identifying strongest classes, weakest classes, and confusion patterns</t>
-  </si>
-  <si>
-    <t>Interpretation is specific to the displayed test results</t>
-  </si>
-  <si>
-    <t>Nour</t>
-  </si>
-  <si>
-    <t>Task 10a: Code</t>
-  </si>
-  <si>
-    <t>Compute precision, recall, and F1 score using the best model</t>
-  </si>
-  <si>
-    <t>Metrics table for each class plus macro/weighted averages if possible</t>
-  </si>
-  <si>
-    <t>Precision, recall, and F1 are correctly displayed for the test set</t>
-  </si>
-  <si>
-    <t>Task 11a: Code</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Implement and run k-fold validation with </t>
+      <t>nesterov=False</t>
+    </r>
+  </si>
+  <si>
+    <t>Baseline model trains successfully and returns usable history/results</t>
+  </si>
+  <si>
+    <t>21-24 JUL</t>
+  </si>
+  <si>
+    <t>Task 7a: Code</t>
+  </si>
+  <si>
+    <t>Plot training and validation accuracy/error for standard transfer learning</t>
+  </si>
+  <si>
+    <t>Accuracy and loss/error plots with labels, legends, and titles</t>
+  </si>
+  <si>
+    <t>Plots are readable and clearly show training vs validation behaviour</t>
+  </si>
+  <si>
+    <t>Task 7b: Report</t>
+  </si>
+  <si>
+    <t>Interpret the baseline training plots</t>
+  </si>
+  <si>
+    <t>Markdown comment on learning trend, overfitting/underfitting, and validation behaviour</t>
+  </si>
+  <si>
+    <t>Comment directly refers to the plotted results</t>
+  </si>
+  <si>
+    <t>Task 8a: Code</t>
+  </si>
+  <si>
+    <t>Run 3 learning-rate experiments across different orders of magnitude</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Results table/plot for 3 learning rates, e.g. </t>
     </r>
     <r>
       <rPr>
@@ -439,7 +383,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>k=3</t>
+      <t>0.1</t>
     </r>
     <r>
       <rPr>
@@ -449,57 +393,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> and two other k values</t>
-    </r>
-  </si>
-  <si>
-    <t>Results table showing metric averages for each k value</t>
-  </si>
-  <si>
-    <t>K-fold validation runs successfully and produces comparable results</t>
-  </si>
-  <si>
-    <t>Task 11b: Report</t>
-  </si>
-  <si>
-    <t>Compare k-fold results against the previous train/test split</t>
-  </si>
-  <si>
-    <t>Markdown comparison of k-fold stability vs earlier test result</t>
-  </si>
-  <si>
-    <t>Comment explains whether model performance is stable or split-sensitive</t>
-  </si>
-  <si>
-    <t>Task 12a: Code</t>
-  </si>
-  <si>
-    <t>Test 3 non-zero momentum values using the best learning rate</t>
-  </si>
-  <si>
-    <t>Results table/plot comparing 3 momentum values</t>
-  </si>
-  <si>
-    <t>All 3 momentum experiments run and are comparable</t>
-  </si>
-  <si>
-    <t>Task 12b: Report</t>
-  </si>
-  <si>
-    <t>Discuss how momentum changed training behaviour/results</t>
-  </si>
-  <si>
-    <t>Markdown explanation of whether momentum improved, worsened, or destabilised training</t>
-  </si>
-  <si>
-    <t>Best momentum value is selected or rejected using evidence</t>
-  </si>
-  <si>
-    <t>Task 13a: Code</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Implement </t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -507,7 +401,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>accelerated_learning()</t>
+      <t>0.01</t>
     </r>
     <r>
       <rPr>
@@ -517,7 +411,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> using precomputed frozen features </t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -525,12 +419,69 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>F(x)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Feature extraction output, accelerated training results, and working </t>
+      <t>0.001</t>
+    </r>
+  </si>
+  <si>
+    <t>All three learning-rate runs complete and are comparable</t>
+  </si>
+  <si>
+    <t>Task 8b: Report</t>
+  </si>
+  <si>
+    <t>Discuss learning-rate experiment results</t>
+  </si>
+  <si>
+    <t>Markdown comparison of the 3 learning rates</t>
+  </si>
+  <si>
+    <t>Best learning rate is clearly selected using evidence from results</t>
+  </si>
+  <si>
+    <t>Task 9: Code</t>
+  </si>
+  <si>
+    <t>Evaluate best learning-rate model on the test set and generate confusion matrix</t>
+  </si>
+  <si>
+    <t>Confusion matrix with class labels</t>
+  </si>
+  <si>
+    <t>Confusion matrix displays correct and incorrect predictions for all 5 classes</t>
+  </si>
+  <si>
+    <t>Task 10b: Report</t>
+  </si>
+  <si>
+    <t>Interpret confusion matrix and classification results</t>
+  </si>
+  <si>
+    <t>Markdown comment identifying strongest classes, weakest classes, and confusion patterns</t>
+  </si>
+  <si>
+    <t>Interpretation is specific to the displayed test results</t>
+  </si>
+  <si>
+    <t>Task 10a: Code</t>
+  </si>
+  <si>
+    <t>Compute precision, recall, and F1 score using the best model</t>
+  </si>
+  <si>
+    <t>Metrics table for each class plus macro/weighted averages if possible</t>
+  </si>
+  <si>
+    <t>Precision, recall, and F1 are correctly displayed for the test set</t>
+  </si>
+  <si>
+    <t>23-26 JUL</t>
+  </si>
+  <si>
+    <t>Task 11a: Code</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement and run k-fold validation with </t>
     </r>
     <r>
       <rPr>
@@ -538,7 +489,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>accelerated_learning()</t>
+      <t>k=3</t>
     </r>
     <r>
       <rPr>
@@ -548,57 +499,57 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> function</t>
-    </r>
-  </si>
-  <si>
-    <t>Function avoids recalculating frozen MobileNetV2 features every epoch and produces valid training results</t>
-  </si>
-  <si>
-    <t>Task 13b: Report</t>
-  </si>
-  <si>
-    <t>Compare accelerated transfer learning against standard transfer learning</t>
-  </si>
-  <si>
-    <t>Plot/table comparing accuracy, loss, and/or training time</t>
-  </si>
-  <si>
-    <t>Discussion explains whether accelerated learning was faster and whether performance changed</t>
-  </si>
-  <si>
-    <t>Task 15: Groupwork</t>
-  </si>
-  <si>
-    <t>Write final contribution breakdown for all members</t>
-  </si>
-  <si>
-    <t>Contribution table/paragraph naming each person’s specific code/report contributions</t>
-  </si>
-  <si>
-    <t>Breakdown aligns with each person’s individual Section 2.1 report</t>
-  </si>
-  <si>
-    <t>Essential Unmarked Tasks</t>
-  </si>
-  <si>
-    <t>No.</t>
-  </si>
-  <si>
-    <t>Task</t>
-  </si>
-  <si>
-    <t>Measurable Output</t>
-  </si>
-  <si>
-    <t>Deadline</t>
-  </si>
-  <si>
-    <t>All members</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Complete </t>
+      <t xml:space="preserve"> and two other k values</t>
+    </r>
+  </si>
+  <si>
+    <t>Results table showing metric averages for each k value</t>
+  </si>
+  <si>
+    <t>K-fold validation runs successfully and produces comparable results</t>
+  </si>
+  <si>
+    <t>Task 11b: Report</t>
+  </si>
+  <si>
+    <t>Compare k-fold results against the previous train/test split</t>
+  </si>
+  <si>
+    <t>Markdown comparison of k-fold stability vs earlier test result</t>
+  </si>
+  <si>
+    <t>Comment explains whether model performance is stable or split-sensitive</t>
+  </si>
+  <si>
+    <t>Task 12a: Code</t>
+  </si>
+  <si>
+    <t>Test 3 non-zero momentum values using the best learning rate</t>
+  </si>
+  <si>
+    <t>Results table/plot comparing 3 momentum values</t>
+  </si>
+  <si>
+    <t>All 3 momentum experiments run and are comparable</t>
+  </si>
+  <si>
+    <t>Task 12b: Report</t>
+  </si>
+  <si>
+    <t>Discuss how momentum changed training behaviour/results</t>
+  </si>
+  <si>
+    <t>Markdown explanation of whether momentum improved, worsened, or destabilised training</t>
+  </si>
+  <si>
+    <t>Best momentum value is selected or rejected using evidence</t>
+  </si>
+  <si>
+    <t>Task 13a: Code</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement </t>
     </r>
     <r>
       <rPr>
@@ -606,7 +557,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>my_team()</t>
+      <t>accelerated_learning()</t>
     </r>
     <r>
       <rPr>
@@ -616,12 +567,28 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> and confirm names/student numbers</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>my_team()</t>
+      <t xml:space="preserve"> using precomputed frozen features </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>F(x)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Feature extraction output, accelerated training results, and working </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>accelerated_learning()</t>
     </r>
     <r>
       <rPr>
@@ -631,85 +598,125 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> returns all group members correctly</t>
-    </r>
-  </si>
-  <si>
-    <t>Notebook integration check</t>
-  </si>
-  <si>
-    <t>All sections are in the correct order under clear task headings</t>
-  </si>
-  <si>
-    <t>Clean run test</t>
-  </si>
-  <si>
-    <t>Notebook runs top-to-bottom without missing variables, broken paths, or hidden dependencies</t>
-  </si>
-  <si>
-    <t>Submitter + all members</t>
-  </si>
-  <si>
-    <t>Final Canvas submission check</t>
-  </si>
-  <si>
-    <t>One person submits; all members verify the uploaded file is correct</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joshua George </t>
-  </si>
-  <si>
-    <t>Joshua George</t>
-  </si>
-  <si>
-    <t>Joshua Oates</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Explain how </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t xml:space="preserve"> function</t>
+    </r>
+  </si>
+  <si>
+    <t>Function avoids recalculating frozen MobileNetV2 features every epoch and produces valid training results</t>
+  </si>
+  <si>
+    <t>Task 13b: Report</t>
+  </si>
+  <si>
+    <t>Compare accelerated transfer learning against standard transfer learning</t>
+  </si>
+  <si>
+    <t>Plot/table comparing accuracy, loss, and/or training time</t>
+  </si>
+  <si>
+    <t>Discussion explains whether accelerated learning was faster and whether performance changed</t>
+  </si>
+  <si>
+    <t>Task 15: Groupwork</t>
+  </si>
+  <si>
+    <t>Write final contribution breakdown for all members</t>
+  </si>
+  <si>
+    <t>Contribution table/paragraph naming each person’s specific code/report contributions</t>
+  </si>
+  <si>
+    <t>Breakdown aligns with each person’s individual Section 2.1 report</t>
+  </si>
+  <si>
+    <t>Essential Unmarked Tasks</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Measurable Output</t>
+  </si>
+  <si>
+    <t>Deadline</t>
+  </si>
+  <si>
+    <t>All members</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Complete </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>transfer_learning()</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t>my_team()</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> works</t>
-    </r>
-  </si>
-  <si>
-    <t>18-21 JUL</t>
-  </si>
-  <si>
-    <t>27-29 JUL</t>
-  </si>
-  <si>
-    <t>21-24 JUL</t>
-  </si>
-  <si>
-    <t>23-26 JUL</t>
+      <t xml:space="preserve"> and confirm names/student numbers</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>my_team()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> returns all group members correctly</t>
+    </r>
+  </si>
+  <si>
+    <t>Notebook integration check</t>
+  </si>
+  <si>
+    <t>All sections are in the correct order under clear task headings</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Clean run test</t>
+  </si>
+  <si>
+    <t>Notebook runs top-to-bottom without missing variables, broken paths, or hidden dependencies</t>
+  </si>
+  <si>
+    <t>Submitter + all members</t>
+  </si>
+  <si>
+    <t>Final Canvas submission check</t>
+  </si>
+  <si>
+    <t>One person submits; all members verify the uploaded file is correct</t>
+  </si>
+  <si>
+    <t>Nour Spear</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -743,12 +750,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF242424"/>
-      <name val="Aptos Narrow"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF242424"/>
@@ -769,8 +770,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -807,6 +827,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -820,7 +846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -838,9 +864,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -867,7 +890,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -876,13 +899,19 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -905,10 +934,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1231,72 +1256,72 @@
   <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="36.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36.5703125" style="3"/>
     <col min="5" max="5" width="35.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36.5703125" style="3"/>
     <col min="7" max="7" width="16.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="36.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="9" customFormat="1" ht="30">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:10" s="8" customFormat="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="45">
-      <c r="A2" s="11">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -1304,31 +1329,31 @@
       <c r="I2" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="30">
+      <c r="A3" s="10">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="30">
-      <c r="A3" s="11">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
@@ -1336,31 +1361,31 @@
       <c r="I3" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J3" s="15" t="s">
-        <v>15</v>
+      <c r="J3" s="21" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="45">
-      <c r="A4" s="11">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="17" t="s">
-        <v>121</v>
+      <c r="F4" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="H4" s="1">
         <v>2</v>
@@ -1368,31 +1393,31 @@
       <c r="I4" s="2">
         <v>0.05</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="45">
-      <c r="A5" s="11">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="H5" s="1">
         <v>2</v>
@@ -1400,31 +1425,31 @@
       <c r="I5" s="2">
         <v>0.05</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="45">
+      <c r="A6" s="10">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="45">
-      <c r="A6" s="11">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="H6" s="1">
         <v>4</v>
@@ -1432,31 +1457,31 @@
       <c r="I6" s="2">
         <v>0.1</v>
       </c>
-      <c r="J6" s="15" t="s">
-        <v>15</v>
+      <c r="J6" s="21" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45">
-      <c r="A7" s="11">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -1464,31 +1489,31 @@
       <c r="I7" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J7" s="15" t="s">
-        <v>15</v>
+      <c r="J7" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="45">
-      <c r="A8" s="11">
+      <c r="A8" s="10">
         <v>7</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -1496,49 +1521,49 @@
       <c r="I8" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J8" s="15" t="s">
-        <v>15</v>
+      <c r="J8" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="11"/>
-      <c r="B9" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="10">
+      <c r="A9" s="10"/>
+      <c r="B9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="9">
         <v>12</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="20">
         <v>0.3</v>
       </c>
-      <c r="J9" s="11"/>
+      <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" ht="42.75">
-      <c r="A10" s="11">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="H10" s="1">
         <v>2</v>
@@ -1546,31 +1571,31 @@
       <c r="I10" s="2">
         <v>0.05</v>
       </c>
-      <c r="J10" s="15" t="s">
-        <v>15</v>
+      <c r="J10" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="45">
-      <c r="A11" s="11">
+      <c r="A11" s="10">
         <v>9</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>118</v>
+      <c r="B11" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="H11" s="1">
         <v>2</v>
@@ -1578,31 +1603,31 @@
       <c r="I11" s="2">
         <v>0.05</v>
       </c>
-      <c r="J11" s="15" t="s">
-        <v>15</v>
+      <c r="J11" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="45">
-      <c r="A12" s="11">
+      <c r="A12" s="10">
         <v>10</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>121</v>
+      <c r="B12" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -1610,31 +1635,31 @@
       <c r="I12" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J12" s="15" t="s">
-        <v>15</v>
+      <c r="J12" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30">
-      <c r="A13" s="11">
+      <c r="A13" s="10">
         <v>11</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>118</v>
+      <c r="B13" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="H13" s="1">
         <v>2</v>
@@ -1642,31 +1667,31 @@
       <c r="I13" s="2">
         <v>0.05</v>
       </c>
-      <c r="J13" s="15" t="s">
-        <v>15</v>
+      <c r="J13" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30">
-      <c r="A14" s="11">
+      <c r="A14" s="10">
         <v>12</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>121</v>
+      <c r="B14" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="H14" s="1">
         <v>2</v>
@@ -1674,31 +1699,31 @@
       <c r="I14" s="2">
         <v>0.05</v>
       </c>
-      <c r="J14" s="15" t="s">
-        <v>15</v>
+      <c r="J14" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="45">
-      <c r="A15" s="11">
+      <c r="A15" s="10">
         <v>13</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>118</v>
+      <c r="B15" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="H15" s="1">
         <v>2</v>
@@ -1706,31 +1731,31 @@
       <c r="I15" s="2">
         <v>0.05</v>
       </c>
-      <c r="J15" s="15" t="s">
-        <v>15</v>
+      <c r="J15" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="45">
-      <c r="A16" s="11">
+      <c r="A16" s="10">
         <v>14</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>121</v>
+      <c r="B16" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
@@ -1738,49 +1763,49 @@
       <c r="I16" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="10"/>
+      <c r="B17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="9">
+        <v>12</v>
+      </c>
+      <c r="I17" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="J17" s="10"/>
+    </row>
+    <row r="18" spans="1:10" ht="30">
+      <c r="A18" s="10">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="11"/>
-      <c r="B17" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="10">
-        <v>12</v>
-      </c>
-      <c r="I17" s="21">
-        <v>0.3</v>
-      </c>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" spans="1:10" ht="30">
-      <c r="A18" s="11">
-        <v>15</v>
-      </c>
       <c r="B18" s="1" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="H18" s="1">
         <v>2</v>
@@ -1788,31 +1813,31 @@
       <c r="I18" s="2">
         <v>0.05</v>
       </c>
-      <c r="J18" s="15" t="s">
-        <v>15</v>
+      <c r="J18" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="30">
-      <c r="A19" s="11">
+      <c r="A19" s="10">
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="H19" s="1">
         <v>2</v>
@@ -1820,31 +1845,31 @@
       <c r="I19" s="2">
         <v>0.05</v>
       </c>
-      <c r="J19" s="15" t="s">
-        <v>15</v>
+      <c r="J19" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="45">
-      <c r="A20" s="11">
+      <c r="A20" s="10">
         <v>17</v>
       </c>
-      <c r="B20" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>121</v>
+      <c r="B20" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -1852,31 +1877,31 @@
       <c r="I20" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J20" s="15" t="s">
-        <v>15</v>
+      <c r="J20" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="30">
-      <c r="A21" s="11">
+      <c r="A21" s="10">
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
@@ -1884,31 +1909,31 @@
       <c r="I21" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J21" s="15" t="s">
-        <v>15</v>
+      <c r="J21" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="45">
-      <c r="A22" s="11">
+      <c r="A22" s="10">
         <v>19</v>
       </c>
-      <c r="B22" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>121</v>
+      <c r="B22" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
@@ -1916,31 +1941,31 @@
       <c r="I22" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J22" s="15" t="s">
-        <v>15</v>
+      <c r="J22" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="45">
-      <c r="A23" s="11">
+      <c r="A23" s="10">
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="H23" s="1">
         <v>4</v>
@@ -1948,31 +1973,31 @@
       <c r="I23" s="2">
         <v>0.1</v>
       </c>
-      <c r="J23" s="15" t="s">
-        <v>15</v>
+      <c r="J23" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="45">
-      <c r="A24" s="11">
+      <c r="A24" s="10">
         <v>21</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>121</v>
+      <c r="B24" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="H24" s="1">
         <v>2</v>
@@ -1980,31 +2005,31 @@
       <c r="I24" s="2">
         <v>0.05</v>
       </c>
-      <c r="J24" s="15" t="s">
-        <v>15</v>
+      <c r="J24" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="45">
-      <c r="A25" s="11">
+      <c r="A25" s="10">
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="H25" s="1">
         <v>3</v>
@@ -2012,138 +2037,138 @@
       <c r="I25" s="2">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="J25" s="15" t="s">
-        <v>15</v>
+      <c r="J25" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="11"/>
-      <c r="B26" s="10" t="s">
+      <c r="A26" s="10"/>
+      <c r="B26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="9">
+        <v>16</v>
+      </c>
+      <c r="I26" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="J26" s="10"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="75">
+      <c r="A30" s="10">
+        <v>23</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G30" s="17">
+        <v>46223</v>
+      </c>
+      <c r="J30" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="30">
+      <c r="A31" s="10">
+        <v>24</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="10">
-        <v>16</v>
-      </c>
-      <c r="I26" s="21">
-        <v>0.4</v>
-      </c>
-      <c r="J26" s="11"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="75">
-      <c r="A30" s="11">
-        <v>23</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G30" s="18">
-        <v>46223</v>
-      </c>
-      <c r="J30" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="30">
-      <c r="A31" s="11">
-        <v>24</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="F31" s="20"/>
-      <c r="G31" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="19" t="s">
-        <v>15</v>
+      <c r="D31" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" s="19"/>
+      <c r="G31" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="18" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="45">
-      <c r="A32" s="11">
+      <c r="A32" s="10">
         <v>25</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G32" s="18">
+        <v>119</v>
+      </c>
+      <c r="G32" s="17">
         <v>46229</v>
       </c>
-      <c r="J32" s="15" t="s">
-        <v>15</v>
+      <c r="J32" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="30">
-      <c r="A33" s="11">
+      <c r="A33" s="10">
         <v>26</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G33" s="18">
+        <v>122</v>
+      </c>
+      <c r="G33" s="17">
         <v>46232</v>
       </c>
-      <c r="J33" s="15" t="s">
-        <v>15</v>
+      <c r="J33" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/CAB320 Work Split.xlsx
+++ b/CAB320 Work Split.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connectqutedu-my.sharepoint.com/personal/n11285915_qut_edu_au/Documents/YR5 SEM1/CAB320/ASSESSMENTS/Assessment 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connectqutedu-my.sharepoint.com/personal/n11285915_qut_edu_au/Documents/Documents/GitHub/CAB320-A2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B585E8A-2441-4AC6-A55D-430ECA22D83B}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{417E6813-091A-43F5-A4AA-7782CB07D10C}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="2040" windowWidth="22605" windowHeight="18570" xr2:uid="{15607E00-DA60-4B2F-9045-4CB7BAC65E04}"/>
+    <workbookView xWindow="11505" yWindow="1560" windowWidth="22815" windowHeight="18165" xr2:uid="{15607E00-DA60-4B2F-9045-4CB7BAC65E04}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="123">
   <si>
     <t>Task No.</t>
   </si>
@@ -657,9 +657,6 @@
   </si>
   <si>
     <t>Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joshua George </t>
   </si>
   <si>
     <t>Joshua George</t>
@@ -709,7 +706,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -731,12 +728,6 @@
       <name val="Arial Unicode MS"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF242424"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -746,7 +737,7 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -820,7 +811,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -834,13 +825,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -867,7 +855,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -876,10 +864,10 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -905,10 +893,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1231,8 +1215,8 @@
   <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="36.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36.5703125" style="3"/>
     <col min="5" max="5" width="35.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -1244,44 +1228,44 @@
     <col min="11" max="16384" width="36.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="9" customFormat="1" ht="30">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:10" s="8" customFormat="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="45">
-      <c r="A2" s="11">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
@@ -1296,7 +1280,7 @@
         <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -1304,16 +1288,16 @@
       <c r="I2" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="30">
-      <c r="A3" s="11">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>117</v>
+      <c r="B3" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -1328,7 +1312,7 @@
         <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
@@ -1336,31 +1320,31 @@
       <c r="I3" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="45">
-      <c r="A4" s="11">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="17" t="s">
-        <v>121</v>
+      <c r="G4" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="H4" s="1">
         <v>2</v>
@@ -1368,16 +1352,16 @@
       <c r="I4" s="2">
         <v>0.05</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="45">
-      <c r="A5" s="11">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>117</v>
+      <c r="B5" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>24</v>
@@ -1392,7 +1376,7 @@
         <v>27</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H5" s="1">
         <v>2</v>
@@ -1400,16 +1384,16 @@
       <c r="I5" s="2">
         <v>0.05</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="45">
-      <c r="A6" s="11">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>117</v>
+      <c r="B6" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
@@ -1424,7 +1408,7 @@
         <v>31</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H6" s="1">
         <v>4</v>
@@ -1432,31 +1416,31 @@
       <c r="I6" s="2">
         <v>0.1</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45">
-      <c r="A7" s="11">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="D7" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="17" t="s">
-        <v>121</v>
+      <c r="G7" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -1464,31 +1448,31 @@
       <c r="I7" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="45">
-      <c r="A8" s="11">
+      <c r="A8" s="10">
         <v>7</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>121</v>
+      <c r="G8" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -1496,34 +1480,34 @@
       <c r="I8" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="11"/>
-      <c r="B9" s="10" t="s">
+      <c r="A9" s="10"/>
+      <c r="B9" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="10">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="9">
         <v>12</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="20">
         <v>0.3</v>
       </c>
-      <c r="J9" s="11"/>
+      <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" ht="42.75">
-      <c r="A10" s="11">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>39</v>
@@ -1538,7 +1522,7 @@
         <v>42</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H10" s="1">
         <v>2</v>
@@ -1546,16 +1530,16 @@
       <c r="I10" s="2">
         <v>0.05</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="45">
-      <c r="A11" s="11">
+      <c r="A11" s="10">
         <v>9</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>118</v>
+      <c r="B11" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>43</v>
@@ -1570,7 +1554,7 @@
         <v>46</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H11" s="1">
         <v>2</v>
@@ -1578,31 +1562,31 @@
       <c r="I11" s="2">
         <v>0.05</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="45">
-      <c r="A12" s="11">
+      <c r="A12" s="10">
         <v>10</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="17" t="s">
+      <c r="B12" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="17" t="s">
-        <v>121</v>
+      <c r="G12" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -1610,16 +1594,16 @@
       <c r="I12" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30">
-      <c r="A13" s="11">
+      <c r="A13" s="10">
         <v>11</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>118</v>
+      <c r="B13" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>51</v>
@@ -1634,7 +1618,7 @@
         <v>54</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H13" s="1">
         <v>2</v>
@@ -1642,31 +1626,31 @@
       <c r="I13" s="2">
         <v>0.05</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30">
-      <c r="A14" s="11">
+      <c r="A14" s="10">
         <v>12</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="17" t="s">
+      <c r="B14" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="17" t="s">
-        <v>121</v>
+      <c r="G14" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="H14" s="1">
         <v>2</v>
@@ -1674,16 +1658,16 @@
       <c r="I14" s="2">
         <v>0.05</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="45">
-      <c r="A15" s="11">
+      <c r="A15" s="10">
         <v>13</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>118</v>
+      <c r="B15" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>59</v>
@@ -1698,7 +1682,7 @@
         <v>62</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H15" s="1">
         <v>2</v>
@@ -1706,31 +1690,31 @@
       <c r="I15" s="2">
         <v>0.05</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="45">
-      <c r="A16" s="11">
+      <c r="A16" s="10">
         <v>14</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="17" t="s">
+      <c r="B16" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="17" t="s">
-        <v>121</v>
+      <c r="G16" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
@@ -1738,34 +1722,34 @@
       <c r="I16" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="11"/>
-      <c r="B17" s="10" t="s">
+      <c r="A17" s="10"/>
+      <c r="B17" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="10">
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="9">
         <v>12</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="20">
         <v>0.3</v>
       </c>
-      <c r="J17" s="11"/>
+      <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" ht="30">
-      <c r="A18" s="11">
+      <c r="A18" s="10">
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>68</v>
@@ -1780,7 +1764,7 @@
         <v>71</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H18" s="1">
         <v>2</v>
@@ -1788,16 +1772,16 @@
       <c r="I18" s="2">
         <v>0.05</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="30">
-      <c r="A19" s="11">
+      <c r="A19" s="10">
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>72</v>
@@ -1812,7 +1796,7 @@
         <v>75</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H19" s="1">
         <v>2</v>
@@ -1820,31 +1804,31 @@
       <c r="I19" s="2">
         <v>0.05</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="45">
-      <c r="A20" s="11">
+      <c r="A20" s="10">
         <v>17</v>
       </c>
-      <c r="B20" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="17" t="s">
+      <c r="B20" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="17" t="s">
-        <v>121</v>
+      <c r="G20" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -1852,16 +1836,16 @@
       <c r="I20" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="30">
-      <c r="A21" s="11">
+      <c r="A21" s="10">
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>80</v>
@@ -1876,7 +1860,7 @@
         <v>83</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
@@ -1884,31 +1868,31 @@
       <c r="I21" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="45">
-      <c r="A22" s="11">
+      <c r="A22" s="10">
         <v>19</v>
       </c>
-      <c r="B22" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="17" t="s">
+      <c r="B22" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G22" s="17" t="s">
-        <v>121</v>
+      <c r="G22" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
@@ -1916,16 +1900,16 @@
       <c r="I22" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="J22" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="45">
-      <c r="A23" s="11">
+      <c r="A23" s="10">
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>88</v>
@@ -1940,7 +1924,7 @@
         <v>91</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H23" s="1">
         <v>4</v>
@@ -1948,31 +1932,31 @@
       <c r="I23" s="2">
         <v>0.1</v>
       </c>
-      <c r="J23" s="15" t="s">
+      <c r="J23" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="45">
-      <c r="A24" s="11">
+      <c r="A24" s="10">
         <v>21</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="17" t="s">
+      <c r="B24" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="G24" s="17" t="s">
-        <v>121</v>
+      <c r="G24" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="H24" s="1">
         <v>2</v>
@@ -1980,16 +1964,16 @@
       <c r="I24" s="2">
         <v>0.05</v>
       </c>
-      <c r="J24" s="15" t="s">
+      <c r="J24" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="45">
-      <c r="A25" s="11">
+      <c r="A25" s="10">
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>96</v>
@@ -2004,7 +1988,7 @@
         <v>99</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H25" s="1">
         <v>3</v>
@@ -2012,59 +1996,59 @@
       <c r="I25" s="2">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="J25" s="15" t="s">
+      <c r="J25" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="11"/>
-      <c r="B26" s="10" t="s">
+      <c r="A26" s="10"/>
+      <c r="B26" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="10">
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="9">
         <v>16</v>
       </c>
-      <c r="I26" s="21">
+      <c r="I26" s="20">
         <v>0.4</v>
       </c>
-      <c r="J26" s="11"/>
+      <c r="J26" s="10"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="11" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="10" t="s">
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="10" t="s">
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="75">
-      <c r="A30" s="11">
+      <c r="A30" s="10">
         <v>23</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -2076,38 +2060,38 @@
       <c r="D30" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="G30" s="18">
+      <c r="G30" s="17">
         <v>46223</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="J30" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="30">
-      <c r="A31" s="11">
+      <c r="A31" s="10">
         <v>24</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F31" s="20"/>
-      <c r="G31" s="19" t="s">
+      <c r="F31" s="19"/>
+      <c r="G31" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="19" t="s">
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="45">
-      <c r="A32" s="11">
+      <c r="A32" s="10">
         <v>25</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -2119,15 +2103,15 @@
       <c r="D32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G32" s="18">
+      <c r="G32" s="17">
         <v>46229</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="J32" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="30">
-      <c r="A33" s="11">
+      <c r="A33" s="10">
         <v>26</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -2139,15 +2123,15 @@
       <c r="D33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G33" s="18">
+      <c r="G33" s="17">
         <v>46232</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="J33" s="14" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/CAB320 Work Split.xlsx
+++ b/CAB320 Work Split.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connectqutedu-my.sharepoint.com/personal/n11285915_qut_edu_au/Documents/Documents/GitHub/CAB320-A2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{417E6813-091A-43F5-A4AA-7782CB07D10C}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5EBE40D-A5C4-45AE-AA5B-3E8DA482E157}"/>
   <bookViews>
     <workbookView xWindow="11505" yWindow="1560" windowWidth="22815" windowHeight="18165" xr2:uid="{15607E00-DA60-4B2F-9045-4CB7BAC65E04}"/>
   </bookViews>
@@ -690,16 +690,16 @@
     </r>
   </si>
   <si>
-    <t>18-21 JUL</t>
-  </si>
-  <si>
-    <t>27-29 JUL</t>
-  </si>
-  <si>
-    <t>21-24 JUL</t>
-  </si>
-  <si>
-    <t>23-26 JUL</t>
+    <t>25-27 MAY</t>
+  </si>
+  <si>
+    <t>18-21 MAY</t>
+  </si>
+  <si>
+    <t>27-29 MAY</t>
+  </si>
+  <si>
+    <t>21-24 MAY</t>
   </si>
 </sst>
 </file>
@@ -1280,7 +1280,7 @@
         <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
@@ -1312,7 +1312,7 @@
         <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H4" s="1">
         <v>2</v>
@@ -1376,7 +1376,7 @@
         <v>27</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H5" s="1">
         <v>2</v>
@@ -1408,7 +1408,7 @@
         <v>31</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H6" s="1">
         <v>4</v>
@@ -1440,7 +1440,7 @@
         <v>34</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -1472,7 +1472,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>42</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H10" s="1">
         <v>2</v>
@@ -1554,7 +1554,7 @@
         <v>46</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H11" s="1">
         <v>2</v>
@@ -1586,7 +1586,7 @@
         <v>50</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -1618,7 +1618,7 @@
         <v>54</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H13" s="1">
         <v>2</v>
@@ -1650,7 +1650,7 @@
         <v>58</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H14" s="1">
         <v>2</v>
@@ -1682,7 +1682,7 @@
         <v>62</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H15" s="1">
         <v>2</v>
@@ -1714,7 +1714,7 @@
         <v>66</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>71</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H18" s="1">
         <v>2</v>
@@ -1796,7 +1796,7 @@
         <v>75</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H19" s="1">
         <v>2</v>
@@ -1828,7 +1828,7 @@
         <v>79</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -1860,7 +1860,7 @@
         <v>83</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
@@ -1892,7 +1892,7 @@
         <v>87</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
@@ -1924,7 +1924,7 @@
         <v>91</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H23" s="1">
         <v>4</v>
@@ -1956,7 +1956,7 @@
         <v>95</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H24" s="1">
         <v>2</v>
@@ -1988,7 +1988,7 @@
         <v>99</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H25" s="1">
         <v>3</v>
@@ -2061,7 +2061,7 @@
         <v>107</v>
       </c>
       <c r="G30" s="17">
-        <v>46223</v>
+        <v>46162</v>
       </c>
       <c r="J30" s="14" t="s">
         <v>15</v>
@@ -2104,7 +2104,7 @@
         <v>111</v>
       </c>
       <c r="G32" s="17">
-        <v>46229</v>
+        <v>46168</v>
       </c>
       <c r="J32" s="14" t="s">
         <v>15</v>
@@ -2124,7 +2124,7 @@
         <v>114</v>
       </c>
       <c r="G33" s="17">
-        <v>46232</v>
+        <v>46171</v>
       </c>
       <c r="J33" s="14" t="s">
         <v>15</v>

--- a/CAB320 Work Split.xlsx
+++ b/CAB320 Work Split.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connectqutedu-my.sharepoint.com/personal/n11285915_qut_edu_au/Documents/Documents/GitHub/CAB320-A2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5EBE40D-A5C4-45AE-AA5B-3E8DA482E157}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{167103F0-35EB-4EFB-A448-C6C50375C6F3}"/>
   <bookViews>
-    <workbookView xWindow="11505" yWindow="1560" windowWidth="22815" windowHeight="18165" xr2:uid="{15607E00-DA60-4B2F-9045-4CB7BAC65E04}"/>
+    <workbookView xWindow="10590" yWindow="0" windowWidth="27915" windowHeight="13395" xr2:uid="{15607E00-DA60-4B2F-9045-4CB7BAC65E04}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="125">
   <si>
     <t>Task No.</t>
   </si>
@@ -700,6 +700,12 @@
   </si>
   <si>
     <t>21-24 MAY</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>In Progress</t>
   </si>
 </sst>
 </file>
@@ -761,7 +767,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -798,6 +804,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -811,7 +829,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -822,9 +840,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -871,6 +886,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1215,8 +1245,8 @@
   <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="36.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36.5703125" style="3"/>
     <col min="5" max="5" width="35.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -1228,40 +1258,40 @@
     <col min="11" max="16384" width="36.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="8" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:10" s="7" customFormat="1">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="45">
-      <c r="A2" s="10">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1288,12 +1318,12 @@
       <c r="I2" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J2" s="14" t="s">
-        <v>15</v>
+      <c r="J2" s="24" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="30">
-      <c r="A3" s="10">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1320,30 +1350,30 @@
       <c r="I3" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J3" s="14" t="s">
-        <v>15</v>
+      <c r="J3" s="24" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="45">
-      <c r="A4" s="10">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>121</v>
       </c>
       <c r="H4" s="1">
@@ -1352,12 +1382,12 @@
       <c r="I4" s="2">
         <v>0.05</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="45">
-      <c r="A5" s="10">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1384,12 +1414,12 @@
       <c r="I5" s="2">
         <v>0.05</v>
       </c>
-      <c r="J5" s="14" t="s">
-        <v>15</v>
+      <c r="J5" s="24" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="45">
-      <c r="A6" s="10">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1416,30 +1446,30 @@
       <c r="I6" s="2">
         <v>0.1</v>
       </c>
-      <c r="J6" s="14" t="s">
-        <v>15</v>
+      <c r="J6" s="24" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45">
-      <c r="A7" s="10">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="15" t="s">
         <v>121</v>
       </c>
       <c r="H7" s="1">
@@ -1448,30 +1478,30 @@
       <c r="I7" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="45">
-      <c r="A8" s="10">
+      <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="15" t="s">
         <v>121</v>
       </c>
       <c r="H8" s="1">
@@ -1480,30 +1510,30 @@
       <c r="I8" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="10"/>
-      <c r="B9" s="9" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="9">
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="8">
         <v>12</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="19">
         <v>0.3</v>
       </c>
-      <c r="J9" s="10"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:10" ht="42.75">
-      <c r="A10" s="10">
+      <c r="A10" s="9">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1530,15 +1560,15 @@
       <c r="I10" s="2">
         <v>0.05</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="45">
-      <c r="A11" s="10">
+      <c r="A11" s="9">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>117</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1562,30 +1592,30 @@
       <c r="I11" s="2">
         <v>0.05</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="45">
-      <c r="A12" s="10">
+      <c r="A12" s="9">
         <v>10</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="15" t="s">
         <v>121</v>
       </c>
       <c r="H12" s="1">
@@ -1594,15 +1624,15 @@
       <c r="I12" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30">
-      <c r="A13" s="10">
+      <c r="A13" s="9">
         <v>11</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>117</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1626,30 +1656,30 @@
       <c r="I13" s="2">
         <v>0.05</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30">
-      <c r="A14" s="10">
+      <c r="A14" s="9">
         <v>12</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="15" t="s">
         <v>121</v>
       </c>
       <c r="H14" s="1">
@@ -1658,15 +1688,15 @@
       <c r="I14" s="2">
         <v>0.05</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="45">
-      <c r="A15" s="10">
+      <c r="A15" s="9">
         <v>13</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>117</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1690,30 +1720,30 @@
       <c r="I15" s="2">
         <v>0.05</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="45">
-      <c r="A16" s="10">
+      <c r="A16" s="9">
         <v>14</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="15" t="s">
         <v>121</v>
       </c>
       <c r="H16" s="1">
@@ -1722,30 +1752,30 @@
       <c r="I16" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="10"/>
-      <c r="B17" s="9" t="s">
+      <c r="A17" s="9"/>
+      <c r="B17" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="9">
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="8">
         <v>12</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="19">
         <v>0.3</v>
       </c>
-      <c r="J17" s="10"/>
+      <c r="J17" s="9"/>
     </row>
     <row r="18" spans="1:10" ht="30">
-      <c r="A18" s="10">
+      <c r="A18" s="9">
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1772,12 +1802,12 @@
       <c r="I18" s="2">
         <v>0.05</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="J18" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="30">
-      <c r="A19" s="10">
+      <c r="A19" s="9">
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1804,30 +1834,30 @@
       <c r="I19" s="2">
         <v>0.05</v>
       </c>
-      <c r="J19" s="14" t="s">
+      <c r="J19" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="45">
-      <c r="A20" s="10">
+      <c r="A20" s="9">
         <v>17</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="15" t="s">
         <v>121</v>
       </c>
       <c r="H20" s="1">
@@ -1836,12 +1866,12 @@
       <c r="I20" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="J20" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="30">
-      <c r="A21" s="10">
+      <c r="A21" s="9">
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1868,30 +1898,30 @@
       <c r="I21" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="J21" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="45">
-      <c r="A22" s="10">
+      <c r="A22" s="9">
         <v>19</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="15" t="s">
         <v>121</v>
       </c>
       <c r="H22" s="1">
@@ -1900,12 +1930,12 @@
       <c r="I22" s="2">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J22" s="14" t="s">
+      <c r="J22" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="45">
-      <c r="A23" s="10">
+      <c r="A23" s="9">
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1932,30 +1962,30 @@
       <c r="I23" s="2">
         <v>0.1</v>
       </c>
-      <c r="J23" s="14" t="s">
+      <c r="J23" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="45">
-      <c r="A24" s="10">
+      <c r="A24" s="9">
         <v>21</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="15" t="s">
         <v>121</v>
       </c>
       <c r="H24" s="1">
@@ -1964,12 +1994,12 @@
       <c r="I24" s="2">
         <v>0.05</v>
       </c>
-      <c r="J24" s="14" t="s">
+      <c r="J24" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="45">
-      <c r="A25" s="10">
+      <c r="A25" s="9">
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1996,102 +2026,106 @@
       <c r="I25" s="2">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="J25" s="14" t="s">
+      <c r="J25" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="10"/>
-      <c r="B26" s="9" t="s">
+      <c r="A26" s="9"/>
+      <c r="B26" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="9">
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="8">
         <v>16</v>
       </c>
-      <c r="I26" s="20">
+      <c r="I26" s="19">
         <v>0.4</v>
       </c>
-      <c r="J26" s="10"/>
+      <c r="J26" s="9"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="10" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="9" t="s">
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="9" t="s">
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="75">
-      <c r="A30" s="10">
+      <c r="A30" s="9">
         <v>23</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="G30" s="17">
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="23">
         <v>46162</v>
       </c>
-      <c r="J30" s="14" t="s">
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="30">
+      <c r="A31" s="9">
+        <v>24</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31" s="18"/>
+      <c r="G31" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="30">
-      <c r="A31" s="10">
-        <v>24</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="18" t="s">
-        <v>15</v>
-      </c>
-    </row>
     <row r="32" spans="1:10" ht="45">
-      <c r="A32" s="10">
+      <c r="A32" s="9">
         <v>25</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -2103,15 +2137,15 @@
       <c r="D32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="16">
         <v>46168</v>
       </c>
-      <c r="J32" s="14" t="s">
+      <c r="J32" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="30">
-      <c r="A33" s="10">
+      <c r="A33" s="9">
         <v>26</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -2123,10 +2157,10 @@
       <c r="D33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="16">
         <v>46171</v>
       </c>
-      <c r="J33" s="14" t="s">
+      <c r="J33" s="13" t="s">
         <v>15</v>
       </c>
     </row>

--- a/CAB320 Work Split.xlsx
+++ b/CAB320 Work Split.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connectqutedu-my.sharepoint.com/personal/n11285915_qut_edu_au/Documents/Documents/GitHub/CAB320-A2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{167103F0-35EB-4EFB-A448-C6C50375C6F3}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{855E250F-1035-4CAF-A9A5-612D2DEF1884}"/>
   <bookViews>
     <workbookView xWindow="10590" yWindow="0" windowWidth="27915" windowHeight="13395" xr2:uid="{15607E00-DA60-4B2F-9045-4CB7BAC65E04}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="126">
   <si>
     <t>Task No.</t>
   </si>
@@ -706,6 +706,9 @@
   </si>
   <si>
     <t>In Progress</t>
+  </si>
+  <si>
+    <t>Complete</t>
   </si>
 </sst>
 </file>
@@ -829,7 +832,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -901,6 +904,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1246,7 +1255,7 @@
   <sheetFormatPr defaultColWidth="36.5703125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36.5703125" style="3"/>
     <col min="5" max="5" width="35.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -1258,7 +1267,7 @@
     <col min="11" max="16384" width="36.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1">
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="30">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1294,96 +1303,96 @@
       <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="20">
         <v>1</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="25">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J2" s="24" t="s">
-        <v>124</v>
+      <c r="J2" s="20" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="30">
       <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="20">
         <v>1</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="25">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J3" s="24" t="s">
-        <v>124</v>
+      <c r="J3" s="20" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="45">
       <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="20">
         <v>2</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="25">
         <v>0.05</v>
       </c>
-      <c r="J4" s="13" t="s">
-        <v>15</v>
+      <c r="J4" s="20" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="45">

--- a/CAB320 Work Split.xlsx
+++ b/CAB320 Work Split.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connectqutedu-my.sharepoint.com/personal/n11285915_qut_edu_au/Documents/Documents/GitHub/CAB320-A2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{855E250F-1035-4CAF-A9A5-612D2DEF1884}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49B80925-1068-4227-9776-89F5AAE007FF}"/>
   <bookViews>
-    <workbookView xWindow="10590" yWindow="0" windowWidth="27915" windowHeight="13395" xr2:uid="{15607E00-DA60-4B2F-9045-4CB7BAC65E04}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{15607E00-DA60-4B2F-9045-4CB7BAC65E04}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="125">
   <si>
     <t>Task No.</t>
   </si>
@@ -665,12 +665,31 @@
     <t>Joshua Oates</t>
   </si>
   <si>
+    <t>25-27 MAY</t>
+  </si>
+  <si>
+    <t>18-21 MAY</t>
+  </si>
+  <si>
+    <t>27-29 MAY</t>
+  </si>
+  <si>
+    <t>21-24 MAY</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Explain how </t>
     </r>
     <r>
       <rPr>
         <b/>
+        <strike/>
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
@@ -680,6 +699,7 @@
     <r>
       <rPr>
         <b/>
+        <strike/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
@@ -688,34 +708,13 @@
       </rPr>
       <t xml:space="preserve"> works</t>
     </r>
-  </si>
-  <si>
-    <t>25-27 MAY</t>
-  </si>
-  <si>
-    <t>18-21 MAY</t>
-  </si>
-  <si>
-    <t>27-29 MAY</t>
-  </si>
-  <si>
-    <t>21-24 MAY</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>Complete</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -756,18 +755,28 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
-    </font>
-    <font>
       <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="9">
@@ -815,7 +824,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -832,7 +841,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -882,10 +891,10 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -903,13 +912,19 @@
     <xf numFmtId="16" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1267,7 +1282,7 @@
     <col min="11" max="16384" width="36.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1" ht="30">
+    <row r="1" spans="1:10" s="7" customFormat="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1319,16 +1334,16 @@
         <v>13</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H2" s="20">
         <v>1</v>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="24">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="30">
@@ -1351,143 +1366,143 @@
         <v>19</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" s="20">
         <v>1</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="24">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="J3" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="45">
       <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="26" t="s">
-        <v>121</v>
+      <c r="G4" s="25" t="s">
+        <v>120</v>
       </c>
       <c r="H4" s="20">
         <v>2</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="24">
         <v>0.05</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="45">
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="G5" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" s="20">
         <v>2</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="24">
         <v>0.05</v>
       </c>
-      <c r="J5" s="24" t="s">
-        <v>124</v>
+      <c r="J5" s="20" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="45">
       <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="G6" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="20">
         <v>4</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="24">
         <v>0.1</v>
       </c>
-      <c r="J6" s="24" t="s">
-        <v>124</v>
+      <c r="J6" s="20" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45">
       <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7" s="15" t="s">
+      <c r="D7" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="G7" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="H7" s="27">
         <v>1</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="28">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="27" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1511,7 +1526,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -1545,32 +1560,32 @@
       <c r="A10" s="9">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="G10" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" s="20">
         <v>2</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="24">
         <v>0.05</v>
       </c>
-      <c r="J10" s="13" t="s">
-        <v>15</v>
+      <c r="J10" s="20" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="45">
@@ -1593,7 +1608,7 @@
         <v>46</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H11" s="1">
         <v>2</v>
@@ -1625,7 +1640,7 @@
         <v>50</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -1657,7 +1672,7 @@
         <v>54</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H13" s="1">
         <v>2</v>
@@ -1689,7 +1704,7 @@
         <v>58</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H14" s="1">
         <v>2</v>
@@ -1721,7 +1736,7 @@
         <v>62</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H15" s="1">
         <v>2</v>
@@ -1753,7 +1768,7 @@
         <v>66</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
@@ -1803,7 +1818,7 @@
         <v>71</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H18" s="1">
         <v>2</v>
@@ -1835,7 +1850,7 @@
         <v>75</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H19" s="1">
         <v>2</v>
@@ -1867,7 +1882,7 @@
         <v>79</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -1899,7 +1914,7 @@
         <v>83</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
@@ -1931,7 +1946,7 @@
         <v>87</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
@@ -1963,7 +1978,7 @@
         <v>91</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H23" s="1">
         <v>4</v>
@@ -1995,7 +2010,7 @@
         <v>95</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H24" s="1">
         <v>2</v>
@@ -2027,7 +2042,7 @@
         <v>99</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H25" s="1">
         <v>3</v>
@@ -2107,7 +2122,7 @@
       <c r="H30" s="22"/>
       <c r="I30" s="22"/>
       <c r="J30" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="30">

--- a/CAB320 Work Split.xlsx
+++ b/CAB320 Work Split.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connectqutedu-my.sharepoint.com/personal/n11285915_qut_edu_au/Documents/Documents/GitHub/CAB320-A2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49B80925-1068-4227-9776-89F5AAE007FF}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="8_{95F0651F-E714-450A-BD31-BCF95EF3D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5173942-F1AA-4178-BDE0-C5215A4AFDF8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{15607E00-DA60-4B2F-9045-4CB7BAC65E04}"/>
+    <workbookView xWindow="-28920" yWindow="1965" windowWidth="29040" windowHeight="15720" xr2:uid="{15607E00-DA60-4B2F-9045-4CB7BAC65E04}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -841,7 +841,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -926,6 +926,9 @@
     </xf>
     <xf numFmtId="10" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1592,63 +1595,63 @@
       <c r="A11" s="9">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="20">
         <v>2</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="24">
         <v>0.05</v>
       </c>
-      <c r="J11" s="13" t="s">
-        <v>15</v>
+      <c r="J11" s="20" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="45">
       <c r="A12" s="9">
         <v>10</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="26">
         <v>1</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="26">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="26" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1656,64 +1659,64 @@
       <c r="A13" s="9">
         <v>11</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="20">
         <v>2</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="24">
         <v>0.05</v>
       </c>
-      <c r="J13" s="13" t="s">
-        <v>15</v>
+      <c r="J13" s="20" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30">
       <c r="A14" s="9">
         <v>12</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="20">
         <v>2</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="24">
         <v>0.05</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>15</v>
+      <c r="J14" s="20" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="45">
@@ -1744,8 +1747,8 @@
       <c r="I15" s="2">
         <v>0.05</v>
       </c>
-      <c r="J15" s="13" t="s">
-        <v>15</v>
+      <c r="J15" s="20" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="45">
